--- a/data/tuning COM translasi roll.xlsx
+++ b/data/tuning COM translasi roll.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,25 +470,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.117</v>
+        <v>0.118</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-35.439</v>
+        <v>3.48</v>
       </c>
       <c r="E2" t="n">
-        <v>195.723</v>
+        <v>199.679</v>
       </c>
       <c r="F2" t="n">
-        <v>-6.958</v>
+        <v>-9.757</v>
       </c>
       <c r="G2" t="n">
-        <v>-63.147</v>
+        <v>-35.52</v>
       </c>
       <c r="H2" t="n">
-        <v>192.596</v>
+        <v>190.981</v>
       </c>
     </row>
     <row r="3">
@@ -496,25 +496,25 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>110.98</v>
+        <v>127.814</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-35.439</v>
+        <v>3.48</v>
       </c>
       <c r="E3" t="n">
-        <v>195.723</v>
+        <v>199.679</v>
       </c>
       <c r="F3" t="n">
-        <v>-6.958</v>
+        <v>-8.766</v>
       </c>
       <c r="G3" t="n">
-        <v>-63.474</v>
+        <v>-37.071</v>
       </c>
       <c r="H3" t="n">
-        <v>192.524</v>
+        <v>193.589</v>
       </c>
     </row>
     <row r="4">
@@ -522,25 +522,25 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>219.353</v>
+        <v>255.803</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-35.439</v>
+        <v>3.48</v>
       </c>
       <c r="E4" t="n">
-        <v>195.723</v>
+        <v>199.679</v>
       </c>
       <c r="F4" t="n">
-        <v>-6.958</v>
+        <v>-8.77</v>
       </c>
       <c r="G4" t="n">
-        <v>-61.645</v>
+        <v>-24.353</v>
       </c>
       <c r="H4" t="n">
-        <v>193.44</v>
+        <v>196.574</v>
       </c>
     </row>
     <row r="5">
@@ -548,25 +548,25 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>332.037</v>
+        <v>383.811</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-35.439</v>
+        <v>3.48</v>
       </c>
       <c r="E5" t="n">
-        <v>195.723</v>
+        <v>199.679</v>
       </c>
       <c r="F5" t="n">
-        <v>-6.958</v>
+        <v>-5.965</v>
       </c>
       <c r="G5" t="n">
-        <v>-53.115</v>
+        <v>-14.935</v>
       </c>
       <c r="H5" t="n">
-        <v>195.514</v>
+        <v>197.94</v>
       </c>
     </row>
     <row r="6">
@@ -574,25 +574,25 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>445.32</v>
+        <v>511.796</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-35.439</v>
+        <v>3.48</v>
       </c>
       <c r="E6" t="n">
-        <v>195.723</v>
+        <v>199.679</v>
       </c>
       <c r="F6" t="n">
-        <v>-6.958</v>
+        <v>-5.965</v>
       </c>
       <c r="G6" t="n">
-        <v>-50.243</v>
+        <v>-7.044</v>
       </c>
       <c r="H6" t="n">
-        <v>195.386</v>
+        <v>198.95</v>
       </c>
     </row>
     <row r="7">
@@ -600,25 +600,25 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>554.929</v>
+        <v>639.796</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-35.439</v>
+        <v>3.48</v>
       </c>
       <c r="E7" t="n">
-        <v>195.723</v>
+        <v>199.679</v>
       </c>
       <c r="F7" t="n">
-        <v>-6.958</v>
+        <v>-5.965</v>
       </c>
       <c r="G7" t="n">
-        <v>-41.27</v>
+        <v>-1.731</v>
       </c>
       <c r="H7" t="n">
-        <v>196.651</v>
+        <v>199.441</v>
       </c>
     </row>
     <row r="8">
@@ -626,25 +626,25 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>666.91</v>
+        <v>767.79</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-35.439</v>
+        <v>3.48</v>
       </c>
       <c r="E8" t="n">
-        <v>195.723</v>
+        <v>199.679</v>
       </c>
       <c r="F8" t="n">
-        <v>-6.958</v>
+        <v>-5.965</v>
       </c>
       <c r="G8" t="n">
-        <v>-37.696</v>
+        <v>3.876</v>
       </c>
       <c r="H8" t="n">
-        <v>196.086</v>
+        <v>199.589</v>
       </c>
     </row>
     <row r="9">
@@ -652,25 +652,25 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>778.899</v>
+        <v>895.783</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-35.439</v>
+        <v>3.48</v>
       </c>
       <c r="E9" t="n">
-        <v>195.723</v>
+        <v>199.679</v>
       </c>
       <c r="F9" t="n">
-        <v>-6.958</v>
+        <v>-5.965</v>
       </c>
       <c r="G9" t="n">
-        <v>-41.155</v>
+        <v>11.138</v>
       </c>
       <c r="H9" t="n">
-        <v>194.729</v>
+        <v>200.656</v>
       </c>
     </row>
     <row r="10">
@@ -678,25 +678,25 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>890.89</v>
+        <v>1023.762</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-35.439</v>
+        <v>3.48</v>
       </c>
       <c r="E10" t="n">
-        <v>195.723</v>
+        <v>199.679</v>
       </c>
       <c r="F10" t="n">
-        <v>-9.802</v>
+        <v>-8.827</v>
       </c>
       <c r="G10" t="n">
-        <v>-38.3</v>
+        <v>18.939</v>
       </c>
       <c r="H10" t="n">
-        <v>195.299</v>
+        <v>200.822</v>
       </c>
     </row>
     <row r="11">
@@ -704,25 +704,25 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1003.038</v>
+        <v>1151.732</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>-35.439</v>
+        <v>3.48</v>
       </c>
       <c r="E11" t="n">
-        <v>195.723</v>
+        <v>199.679</v>
       </c>
       <c r="F11" t="n">
-        <v>-9.789999999999999</v>
+        <v>-11.707</v>
       </c>
       <c r="G11" t="n">
-        <v>-33.51</v>
+        <v>22.928</v>
       </c>
       <c r="H11" t="n">
-        <v>195.892</v>
+        <v>200.54</v>
       </c>
     </row>
     <row r="12">
@@ -730,25 +730,25 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1115.201</v>
+        <v>1279.782</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-35.439</v>
+        <v>3.48</v>
       </c>
       <c r="E12" t="n">
-        <v>195.723</v>
+        <v>199.679</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.958</v>
+        <v>-8.833</v>
       </c>
       <c r="G12" t="n">
-        <v>-33.506</v>
+        <v>23.439</v>
       </c>
       <c r="H12" t="n">
-        <v>196.015</v>
+        <v>200.233</v>
       </c>
     </row>
     <row r="13">
@@ -756,25 +756,25 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1227.25</v>
+        <v>1407.761</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>-35.439</v>
+        <v>3.48</v>
       </c>
       <c r="E13" t="n">
-        <v>195.723</v>
+        <v>199.679</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.958</v>
+        <v>-8.827</v>
       </c>
       <c r="G13" t="n">
-        <v>-33.506</v>
+        <v>21.209</v>
       </c>
       <c r="H13" t="n">
-        <v>196.015</v>
+        <v>199.981</v>
       </c>
     </row>
     <row r="14">
@@ -782,25 +782,25 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1341.705</v>
+        <v>1535.738</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-35.439</v>
+        <v>3.48</v>
       </c>
       <c r="E14" t="n">
-        <v>195.723</v>
+        <v>199.679</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.958</v>
+        <v>-8.824</v>
       </c>
       <c r="G14" t="n">
-        <v>-33.171</v>
+        <v>12.877</v>
       </c>
       <c r="H14" t="n">
-        <v>196.007</v>
+        <v>200.485</v>
       </c>
     </row>
     <row r="15">
@@ -808,25 +808,25 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1450.871</v>
+        <v>1663.765</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>-35.439</v>
+        <v>3.48</v>
       </c>
       <c r="E15" t="n">
-        <v>195.723</v>
+        <v>199.679</v>
       </c>
       <c r="F15" t="n">
-        <v>-6.958</v>
+        <v>-8.821</v>
       </c>
       <c r="G15" t="n">
-        <v>-33.171</v>
+        <v>7.513</v>
       </c>
       <c r="H15" t="n">
-        <v>196.007</v>
+        <v>200.494</v>
       </c>
     </row>
     <row r="16">
@@ -834,25 +834,25 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1562.965</v>
+        <v>1791.766</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>-35.439</v>
+        <v>3.48</v>
       </c>
       <c r="E16" t="n">
-        <v>195.723</v>
+        <v>199.679</v>
       </c>
       <c r="F16" t="n">
-        <v>-6.958</v>
+        <v>-8.819000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>-36.037</v>
+        <v>1.89</v>
       </c>
       <c r="H16" t="n">
-        <v>195.403</v>
+        <v>200.501</v>
       </c>
     </row>
     <row r="17">
@@ -860,25 +860,25 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1674.52</v>
+        <v>1919.741</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>-35.439</v>
+        <v>3.48</v>
       </c>
       <c r="E17" t="n">
-        <v>195.723</v>
+        <v>199.679</v>
       </c>
       <c r="F17" t="n">
-        <v>-6.958</v>
+        <v>-8.819000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>-36.037</v>
+        <v>-1.061</v>
       </c>
       <c r="H17" t="n">
-        <v>195.403</v>
+        <v>200.508</v>
       </c>
     </row>
     <row r="18">
@@ -886,77 +886,25 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1789.201</v>
+        <v>2047.728</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>-35.439</v>
+        <v>3.48</v>
       </c>
       <c r="E18" t="n">
-        <v>195.723</v>
+        <v>199.679</v>
       </c>
       <c r="F18" t="n">
-        <v>-6.958</v>
+        <v>-8.819000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>-36.037</v>
+        <v>-4.011</v>
       </c>
       <c r="H18" t="n">
-        <v>195.403</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="n">
-        <v>1899.093</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>-35.439</v>
-      </c>
-      <c r="E19" t="n">
-        <v>195.723</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-6.958</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-36.037</v>
-      </c>
-      <c r="H19" t="n">
-        <v>195.403</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="n">
-        <v>2011.029</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>-35.439</v>
-      </c>
-      <c r="E20" t="n">
-        <v>195.723</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-6.958</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-36.037</v>
-      </c>
-      <c r="H20" t="n">
-        <v>195.403</v>
+        <v>200.464</v>
       </c>
     </row>
   </sheetData>

--- a/data/tuning COM translasi roll.xlsx
+++ b/data/tuning COM translasi roll.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,25 +470,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.118</v>
+        <v>0.108</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>3.48</v>
+        <v>-35.949</v>
       </c>
       <c r="E2" t="n">
-        <v>199.679</v>
+        <v>190.623</v>
       </c>
       <c r="F2" t="n">
-        <v>-9.757</v>
+        <v>-9.885</v>
       </c>
       <c r="G2" t="n">
-        <v>-35.52</v>
+        <v>-62.639</v>
       </c>
       <c r="H2" t="n">
-        <v>190.981</v>
+        <v>187.567</v>
       </c>
     </row>
     <row r="3">
@@ -496,25 +496,25 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>127.814</v>
+        <v>108.046</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>3.48</v>
+        <v>-35.949</v>
       </c>
       <c r="E3" t="n">
-        <v>199.679</v>
+        <v>190.623</v>
       </c>
       <c r="F3" t="n">
-        <v>-8.766</v>
+        <v>-9.885</v>
       </c>
       <c r="G3" t="n">
-        <v>-37.071</v>
+        <v>-62.639</v>
       </c>
       <c r="H3" t="n">
-        <v>193.589</v>
+        <v>187.567</v>
       </c>
     </row>
     <row r="4">
@@ -522,25 +522,25 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>255.803</v>
+        <v>218.778</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>3.48</v>
+        <v>-35.949</v>
       </c>
       <c r="E4" t="n">
-        <v>199.679</v>
+        <v>190.623</v>
       </c>
       <c r="F4" t="n">
-        <v>-8.77</v>
+        <v>-9.885</v>
       </c>
       <c r="G4" t="n">
-        <v>-24.353</v>
+        <v>-63.678</v>
       </c>
       <c r="H4" t="n">
-        <v>196.574</v>
+        <v>187.354</v>
       </c>
     </row>
     <row r="5">
@@ -548,25 +548,25 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>383.811</v>
+        <v>330.938</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>3.48</v>
+        <v>-35.949</v>
       </c>
       <c r="E5" t="n">
-        <v>199.679</v>
+        <v>190.623</v>
       </c>
       <c r="F5" t="n">
-        <v>-5.965</v>
+        <v>-9.878</v>
       </c>
       <c r="G5" t="n">
-        <v>-14.935</v>
+        <v>-56.696</v>
       </c>
       <c r="H5" t="n">
-        <v>197.94</v>
+        <v>189.804</v>
       </c>
     </row>
     <row r="6">
@@ -574,25 +574,25 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>511.796</v>
+        <v>442.889</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>3.48</v>
+        <v>-35.949</v>
       </c>
       <c r="E6" t="n">
-        <v>199.679</v>
+        <v>190.623</v>
       </c>
       <c r="F6" t="n">
-        <v>-5.965</v>
+        <v>-9.852</v>
       </c>
       <c r="G6" t="n">
-        <v>-7.044</v>
+        <v>-53.873</v>
       </c>
       <c r="H6" t="n">
-        <v>198.95</v>
+        <v>189.797</v>
       </c>
     </row>
     <row r="7">
@@ -600,25 +600,25 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>639.796</v>
+        <v>556.562</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>3.48</v>
+        <v>-35.949</v>
       </c>
       <c r="E7" t="n">
-        <v>199.679</v>
+        <v>190.623</v>
       </c>
       <c r="F7" t="n">
-        <v>-5.965</v>
+        <v>-9.823</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.731</v>
+        <v>-47.897</v>
       </c>
       <c r="H7" t="n">
-        <v>199.441</v>
+        <v>190.521</v>
       </c>
     </row>
     <row r="8">
@@ -626,25 +626,25 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>767.79</v>
+        <v>666.772</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>3.48</v>
+        <v>-35.949</v>
       </c>
       <c r="E8" t="n">
-        <v>199.679</v>
+        <v>190.623</v>
       </c>
       <c r="F8" t="n">
-        <v>-5.965</v>
+        <v>-7</v>
       </c>
       <c r="G8" t="n">
-        <v>3.876</v>
+        <v>-43.784</v>
       </c>
       <c r="H8" t="n">
-        <v>199.589</v>
+        <v>190.947</v>
       </c>
     </row>
     <row r="9">
@@ -652,25 +652,25 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>895.783</v>
+        <v>778.6</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>3.48</v>
+        <v>-35.949</v>
       </c>
       <c r="E9" t="n">
-        <v>199.679</v>
+        <v>190.623</v>
       </c>
       <c r="F9" t="n">
-        <v>-5.965</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>11.138</v>
+        <v>-42.782</v>
       </c>
       <c r="H9" t="n">
-        <v>200.656</v>
+        <v>190.258</v>
       </c>
     </row>
     <row r="10">
@@ -678,25 +678,25 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1023.762</v>
+        <v>891.026</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>3.48</v>
+        <v>-35.949</v>
       </c>
       <c r="E10" t="n">
-        <v>199.679</v>
+        <v>190.623</v>
       </c>
       <c r="F10" t="n">
-        <v>-8.827</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>18.939</v>
+        <v>-37.214</v>
       </c>
       <c r="H10" t="n">
-        <v>200.822</v>
+        <v>191.654</v>
       </c>
     </row>
     <row r="11">
@@ -704,25 +704,25 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1151.732</v>
+        <v>1004.946</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>3.48</v>
+        <v>-35.949</v>
       </c>
       <c r="E11" t="n">
-        <v>199.679</v>
+        <v>190.623</v>
       </c>
       <c r="F11" t="n">
-        <v>-11.707</v>
+        <v>-9.757</v>
       </c>
       <c r="G11" t="n">
-        <v>22.928</v>
+        <v>-35.52</v>
       </c>
       <c r="H11" t="n">
-        <v>200.54</v>
+        <v>190.981</v>
       </c>
     </row>
     <row r="12">
@@ -730,25 +730,25 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1279.782</v>
+        <v>1114.729</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>3.48</v>
+        <v>-35.949</v>
       </c>
       <c r="E12" t="n">
-        <v>199.679</v>
+        <v>190.623</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.833</v>
+        <v>-9.757</v>
       </c>
       <c r="G12" t="n">
-        <v>23.439</v>
+        <v>-35.52</v>
       </c>
       <c r="H12" t="n">
-        <v>200.233</v>
+        <v>190.981</v>
       </c>
     </row>
     <row r="13">
@@ -756,25 +756,25 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1407.761</v>
+        <v>1226.709</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>3.48</v>
+        <v>-35.949</v>
       </c>
       <c r="E13" t="n">
-        <v>199.679</v>
+        <v>190.623</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.827</v>
+        <v>-9.757</v>
       </c>
       <c r="G13" t="n">
-        <v>21.209</v>
+        <v>-35.52</v>
       </c>
       <c r="H13" t="n">
-        <v>199.981</v>
+        <v>190.981</v>
       </c>
     </row>
     <row r="14">
@@ -782,25 +782,25 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1535.738</v>
+        <v>1338.976</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>3.48</v>
+        <v>-35.949</v>
       </c>
       <c r="E14" t="n">
-        <v>199.679</v>
+        <v>190.623</v>
       </c>
       <c r="F14" t="n">
-        <v>-8.824</v>
+        <v>-9.757</v>
       </c>
       <c r="G14" t="n">
-        <v>12.877</v>
+        <v>-35.52</v>
       </c>
       <c r="H14" t="n">
-        <v>200.485</v>
+        <v>190.981</v>
       </c>
     </row>
     <row r="15">
@@ -808,25 +808,25 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1663.765</v>
+        <v>1450.743</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>3.48</v>
+        <v>-35.949</v>
       </c>
       <c r="E15" t="n">
-        <v>199.679</v>
+        <v>190.623</v>
       </c>
       <c r="F15" t="n">
-        <v>-8.821</v>
+        <v>-9.757</v>
       </c>
       <c r="G15" t="n">
-        <v>7.513</v>
+        <v>-35.52</v>
       </c>
       <c r="H15" t="n">
-        <v>200.494</v>
+        <v>190.981</v>
       </c>
     </row>
     <row r="16">
@@ -834,25 +834,25 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1791.766</v>
+        <v>1562.916</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.48</v>
+        <v>-35.949</v>
       </c>
       <c r="E16" t="n">
-        <v>199.679</v>
+        <v>190.623</v>
       </c>
       <c r="F16" t="n">
-        <v>-8.819000000000001</v>
+        <v>-7</v>
       </c>
       <c r="G16" t="n">
-        <v>1.89</v>
+        <v>-35.518</v>
       </c>
       <c r="H16" t="n">
-        <v>200.501</v>
+        <v>191.103</v>
       </c>
     </row>
     <row r="17">
@@ -860,25 +860,25 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1919.741</v>
+        <v>1674.744</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>3.48</v>
+        <v>-35.949</v>
       </c>
       <c r="E17" t="n">
-        <v>199.679</v>
+        <v>190.623</v>
       </c>
       <c r="F17" t="n">
-        <v>-8.819000000000001</v>
+        <v>-9.757</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.061</v>
+        <v>-35.52</v>
       </c>
       <c r="H17" t="n">
-        <v>200.508</v>
+        <v>190.981</v>
       </c>
     </row>
     <row r="18">
@@ -886,25 +886,77 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2047.728</v>
+        <v>1786.682</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.48</v>
+        <v>-35.949</v>
       </c>
       <c r="E18" t="n">
-        <v>199.679</v>
+        <v>190.623</v>
       </c>
       <c r="F18" t="n">
-        <v>-8.819000000000001</v>
+        <v>-9.757</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.011</v>
+        <v>-35.52</v>
       </c>
       <c r="H18" t="n">
-        <v>200.464</v>
+        <v>190.981</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1902.067</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-35.949</v>
+      </c>
+      <c r="E19" t="n">
+        <v>190.623</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-9.757</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-35.52</v>
+      </c>
+      <c r="H19" t="n">
+        <v>190.981</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>2010.671</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-35.949</v>
+      </c>
+      <c r="E20" t="n">
+        <v>190.623</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-9.757</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-35.52</v>
+      </c>
+      <c r="H20" t="n">
+        <v>190.981</v>
       </c>
     </row>
   </sheetData>
